--- a/Doc/journal_de_travail.xlsx
+++ b/Doc/journal_de_travail.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Tableau de bord" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Journal'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tableau de bord'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Journal'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tableau de bord'!$A$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -92,6 +92,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -731,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -926,32 +929,108 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Fix(manual)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Fix(manual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Total du jour</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>0h05 (5 min)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Update get_commit.sh</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Update get_commit.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Total du jour</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0h00 (0 min)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
-  <mergeCells count="3">
+  <autoFilter ref="A1:E19"/>
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -994,22 +1073,22 @@
           <t>Total (h:min)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Cumul (h)</t>
         </is>
@@ -1032,13 +1111,13 @@
           <t>0h00</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Jours suivis</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1066,7 +1145,7 @@
           <t>0h00</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Temps total</t>
         </is>
@@ -1102,14 +1181,14 @@
           <t>0h05</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Moyenne / jour</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0h02</t>
+          <t>0h01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1122,7 +1201,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="F5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0h00</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Jour le plus charge</t>
         </is>
@@ -1132,9 +1227,17 @@
           <t>25/03/2026 (0h05)</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.08</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Doc/journal_de_travail.xlsx
+++ b/Doc/journal_de_travail.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Tableau de bord" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Journal'!$A$1:$E$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tableau de bord'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Journal'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tableau de bord'!$A$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,18 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
   </fonts>
@@ -81,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -96,6 +108,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -174,7 +195,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -319,6 +339,14 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
           <cat>
             <numRef>
               <f>'Tableau de bord'!$A$2:$A$5</f>
@@ -327,6 +355,230 @@
           <val>
             <numRef>
               <f>'Tableau de bord'!$J$2:$J$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <smooth val="1"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Heures</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Charge par jour (heures)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tableau de bord'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Tableau de bord'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tableau de bord'!$C$2:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Heures</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cumul des heures</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Tableau de bord'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Tableau de bord'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Tableau de bord'!$J$2:$J$6</f>
             </numRef>
           </val>
         </ser>
@@ -437,6 +689,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -734,12 +1030,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
   </cols>
@@ -772,66 +1068,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr"/>
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Initial commit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Add script to extract Git logs and generate reports</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Add script to extract Git logs and generate reports This script extracts Git commit logs since a specified date and formats them into a CSV file. It also converts the CSV into an XLSX file, including charts for visual representation.</t>
+      <c r="A4" s="9" t="inlineStr"/>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Add script to extract Git journal and generate reports</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Add script to extract Git journal and generate reports This script extracts Git commit journal since a specified date and formats them into a CSV file. It also converts the CSV into an XLSX file, including charts for visual representation.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Total du jour</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>0h00 (0 min)</t>
         </is>
@@ -847,43 +1143,43 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Update comment in get_commit.sh for clarity</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Update comment in get_commit.sh for clarity Removed the note about overwriting the existing file in the header comment.</t>
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour comment in get_commit.sh for clarity</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour comment in get_commit.sh for clarity Removed the note about overwriting the existing file in the header comment.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Total du jour</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>0h00 (0 min)</t>
         </is>
@@ -899,53 +1195,53 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Feat(Manualle): possible d'ajout a la main</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Fonctionnalité (Manualle) : possible d'ajout a la main</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>[5]</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>[DONE]</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Feat(Manualle): possible d'ajout a la main</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Fonctionnalité (Manualle) : possible d'ajout a la main</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Fix(manual)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Fix(manual)</t>
         </is>
@@ -953,12 +1249,12 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Total du jour</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>0h05 (5 min)</t>
         </is>
@@ -974,64 +1270,186 @@
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Update get_commit.sh</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Update get_commit.sh</t>
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour get_commit.sh</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour get_commit.sh</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Fix(lisez-moi)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Fix(lisez-moi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Feat(contriubut)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Feat(contriubut)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Total du jour</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>0h00 (0 min)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour get_commit.sh</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour get_commit.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour lisez-moi.md</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>mise à jour lisez-moi.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Total du jour</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>0h00 (0 min)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
-  <mergeCells count="4">
+  <autoFilter ref="A1:E26"/>
+  <mergeCells count="5">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1043,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1053,42 +1471,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Total (min)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Total (h)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Total (h:min)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Cumul (h)</t>
         </is>
@@ -1111,13 +1529,13 @@
           <t>0h00</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Jours suivis</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1145,7 +1563,7 @@
           <t>0h00</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Temps total</t>
         </is>
@@ -1181,7 +1599,7 @@
           <t>0h05</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Moyenne / jour</t>
         </is>
@@ -1217,9 +1635,9 @@
           <t>0h00</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Jour le plus charge</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Jour le plus chargé</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1236,8 +1654,34 @@
         <v>0.08</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0h00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
